--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_11.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03232082316829615</v>
+        <v>0.02803418405329522</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008460085995390417</v>
+        <v>0.008452553723509622</v>
       </c>
       <c r="C2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>47015499</v>
+        <v>4033327</v>
       </c>
       <c r="L2" t="n">
-        <v>23823870</v>
+        <v>1655598</v>
       </c>
       <c r="M2" t="n">
-        <v>5336782</v>
+        <v>310192</v>
       </c>
       <c r="N2" t="n">
-        <v>230624</v>
+        <v>5963</v>
       </c>
       <c r="O2" t="n">
-        <v>3123302</v>
+        <v>149576</v>
       </c>
       <c r="P2" t="n">
-        <v>1232485</v>
+        <v>42938</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999874234199524</v>
+        <v>0.9999811053276062</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8104573488235474</v>
+        <v>0.717011570930481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.66251540184021</v>
+        <v>0.5339586138725281</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5782999992370605</v>
+        <v>0.4001227915287018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.175100639462471</v>
+        <v>0.03960336744785309</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6380312442779541</v>
+        <v>0.4338504076004028</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7492651343345642</v>
+        <v>0.5871943831443787</v>
       </c>
       <c r="X2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53175479</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33163018</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8850920</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>652300</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5064045</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982621</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9557910561561584</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116975665092468</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578632473945618</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6612526774406433</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019046425819397</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314442276954651</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00854795471875998</v>
+        <v>0.007264160137855754</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00202627677219498</v>
+        <v>0.002025028638077513</v>
       </c>
       <c r="C3" t="n">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>47015499</v>
+        <v>4033327</v>
       </c>
       <c r="E3" t="n">
-        <v>8174963</v>
+        <v>909028</v>
       </c>
       <c r="F3" t="n">
-        <v>290800</v>
+        <v>39519</v>
       </c>
       <c r="G3" t="n">
-        <v>34939</v>
+        <v>3895</v>
       </c>
       <c r="H3" t="n">
-        <v>20207</v>
+        <v>2622</v>
       </c>
       <c r="I3" t="n">
-        <v>1813</v>
+        <v>307</v>
       </c>
       <c r="J3" t="n">
-        <v>111056427</v>
+        <v>10069500</v>
       </c>
       <c r="K3" t="n">
-        <v>114517316</v>
+        <v>9835422</v>
       </c>
       <c r="L3" t="n">
-        <v>132461982</v>
+        <v>11631081</v>
       </c>
       <c r="M3" t="n">
-        <v>166829700</v>
+        <v>15006567</v>
       </c>
       <c r="N3" t="n">
-        <v>178977256</v>
+        <v>16181288</v>
       </c>
       <c r="O3" t="n">
-        <v>173660344</v>
+        <v>15708234</v>
       </c>
       <c r="P3" t="n">
-        <v>178509428</v>
+        <v>16191882</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8465417623519897</v>
+        <v>0.8084903359413147</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6535437703132629</v>
+        <v>0.4957019686698914</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5166351795196533</v>
+        <v>0.3284599483013153</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2335494458675385</v>
+        <v>0.0661768764257431</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5558525323867798</v>
+        <v>0.2918111979961395</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5788129568099976</v>
+        <v>0.2214075028896332</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53175479</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2192163</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>94407</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75574</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>111057309</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>123053320</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141385832</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>169254833</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179729565</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174881471</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178775944</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9574558138847351</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097381830215454</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8568266034126282</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6605743765830994</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9012455940246582</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311000108718872</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07133530783649746</v>
+        <v>0.06325930304986038</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03198645682554076</v>
+        <v>0.03196808737360584</v>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>10088669</v>
+        <v>1421742</v>
       </c>
       <c r="E4" t="n">
-        <v>23823870</v>
+        <v>1655598</v>
       </c>
       <c r="F4" t="n">
-        <v>2098072</v>
+        <v>210650</v>
       </c>
       <c r="G4" t="n">
-        <v>172216</v>
+        <v>21665</v>
       </c>
       <c r="H4" t="n">
-        <v>242110</v>
+        <v>27177</v>
       </c>
       <c r="I4" t="n">
-        <v>28367</v>
+        <v>3055</v>
       </c>
       <c r="J4" t="n">
-        <v>882</v>
+        <v>120</v>
       </c>
       <c r="K4" t="n">
-        <v>10995572</v>
+        <v>1591864</v>
       </c>
       <c r="L4" t="n">
-        <v>12135852</v>
+        <v>1445013</v>
       </c>
       <c r="M4" t="n">
-        <v>3891615</v>
+        <v>465050</v>
       </c>
       <c r="N4" t="n">
-        <v>1086470</v>
+        <v>144605</v>
       </c>
       <c r="O4" t="n">
-        <v>1771916</v>
+        <v>195188</v>
       </c>
       <c r="P4" t="n">
-        <v>412440</v>
+        <v>30186</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999937415122986</v>
+        <v>0.9999905228614807</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8281066417694092</v>
+        <v>0.7600081562995911</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6579990386962891</v>
+        <v>0.5141196250915527</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5457311868667603</v>
+        <v>0.3607670068740845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2001450955867767</v>
+        <v>0.04955229908227921</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5941135883331299</v>
+        <v>0.3489295840263367</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6531007289886475</v>
+        <v>0.3215655386447906</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2297185</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33163018</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>918333</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61374</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12703</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>753</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2459568</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3212002</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1466482</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>334161</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>550789</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145924</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566227197647095</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107168316841125</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8573446273803711</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.660913348197937</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9015750288963318</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931272029876709</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>653680</v>
+        <v>126088</v>
       </c>
       <c r="E5" t="n">
-        <v>3149042</v>
+        <v>397670</v>
       </c>
       <c r="F5" t="n">
-        <v>5336782</v>
+        <v>310192</v>
       </c>
       <c r="G5" t="n">
-        <v>336616</v>
+        <v>36925</v>
       </c>
       <c r="H5" t="n">
-        <v>760627</v>
+        <v>64142</v>
       </c>
       <c r="I5" t="n">
-        <v>93055</v>
+        <v>9355</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8522813</v>
+        <v>955387</v>
       </c>
       <c r="L5" t="n">
-        <v>12629496</v>
+        <v>1684308</v>
       </c>
       <c r="M5" t="n">
-        <v>4993103</v>
+        <v>634191</v>
       </c>
       <c r="N5" t="n">
-        <v>756850</v>
+        <v>84144</v>
       </c>
       <c r="O5" t="n">
-        <v>2495638</v>
+        <v>363002</v>
       </c>
       <c r="P5" t="n">
-        <v>896847</v>
+        <v>150994</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999951124191284</v>
+        <v>0.9999926686286926</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8921940922737122</v>
+        <v>0.8448312282562256</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8632135391235352</v>
+        <v>0.8093737363815308</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9509270191192627</v>
+        <v>0.9330384135246277</v>
       </c>
       <c r="U5" t="n">
-        <v>0.989818811416626</v>
+        <v>0.9860655069351196</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9764290452003479</v>
+        <v>0.9659972190856934</v>
       </c>
       <c r="W5" t="n">
-        <v>0.992768406867981</v>
+        <v>0.9889631867408752</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89547</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>950629</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8850920</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>110142</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321676</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6971</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2362833</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3290348</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1478965</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>335174</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>554895</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146711</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733644127845764</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964085578918457</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837313890457153</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963030815124512</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938929677009583</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983837008476257</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>174691</v>
+        <v>23565</v>
       </c>
       <c r="E6" t="n">
-        <v>228950</v>
+        <v>26993</v>
       </c>
       <c r="F6" t="n">
-        <v>239095</v>
+        <v>25838</v>
       </c>
       <c r="G6" t="n">
-        <v>230624</v>
+        <v>5963</v>
       </c>
       <c r="H6" t="n">
-        <v>100875</v>
+        <v>6875</v>
       </c>
       <c r="I6" t="n">
-        <v>13099</v>
+        <v>850</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>72280</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59401</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>121076</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>652300</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77120</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5297</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>73288</v>
+        <v>18899</v>
       </c>
       <c r="E7" t="n">
-        <v>527236</v>
+        <v>99279</v>
       </c>
       <c r="F7" t="n">
-        <v>1148194</v>
+        <v>162808</v>
       </c>
       <c r="G7" t="n">
-        <v>470590</v>
+        <v>65375</v>
       </c>
       <c r="H7" t="n">
-        <v>3123302</v>
+        <v>149576</v>
       </c>
       <c r="I7" t="n">
-        <v>276106</v>
+        <v>16619</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>248</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8917</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>329015</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>84142</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5064045</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132573</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>5244</v>
+        <v>1570</v>
       </c>
       <c r="E8" t="n">
-        <v>55661</v>
+        <v>12043</v>
       </c>
       <c r="F8" t="n">
-        <v>115454</v>
+        <v>26235</v>
       </c>
       <c r="G8" t="n">
-        <v>72109</v>
+        <v>16745</v>
       </c>
       <c r="H8" t="n">
-        <v>648097</v>
+        <v>94372</v>
       </c>
       <c r="I8" t="n">
-        <v>1232485</v>
+        <v>42938</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>892</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3651</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2929</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138931</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982621</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
